--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCION 94/LTAIPT_A94F1.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCION 94/LTAIPT_A94F1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="74">
   <si>
     <t>50922</t>
   </si>
@@ -226,16 +226,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>C8D19E85D14B7A492232FD5FE64511EE</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>C7AC999DB1B5A4A2</t>
   </si>
   <si>
     <t/>
@@ -244,10 +235,7 @@
     <t>Unidad de Transparencia</t>
   </si>
   <si>
-    <t>27/01/2023</t>
-  </si>
-  <si>
-    <t>En el periodo del 01 de julio del 2022 al 31 de diciembre del 2022, el Colegio de Bachilleres del Estado de Tlaxcala no realizó ningún procedimiento de reserva de información pública.</t>
+    <t>En el periodo del 01 de enero del 2023 al 30 de marzo del 2023, el Colegio de Bachilleres del Estado de Tlaxcala no realizó ningún procedimiento de reserva de información pública.</t>
   </si>
 </sst>
 </file>
@@ -324,7 +312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -338,6 +326,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1017,92 +1011,92 @@
       <c r="A8" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B8" s="2">
+        <v>2023</v>
+      </c>
+      <c r="C8" s="6">
+        <v>44927</v>
+      </c>
+      <c r="D8" s="6">
+        <v>45015</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="AB8" s="6">
+        <v>45001</v>
+      </c>
+      <c r="AC8" s="6">
+        <v>45001</v>
+      </c>
+      <c r="AD8" s="7" t="s">
         <v>73</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AC8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AD8" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
   </sheetData>
